--- a/Alwars.xlsx
+++ b/Alwars.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\The Spirtuals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mongo\mongodb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916166CC-10A9-47FE-A953-9F50B616DF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FC71F0-AAB4-470D-97DA-24C11CCA7DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t xml:space="preserve">Alwars </t>
   </si>
@@ -755,4 +756,55 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{895F2931-AC63-4E13-B040-C7D69F46F3F4}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6">
+      <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.6">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.6">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.6">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Alwars.xlsx
+++ b/Alwars.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mongo\mongodb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FC71F0-AAB4-470D-97DA-24C11CCA7DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AD5C7E-B2BA-405A-A311-148D769D19CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t xml:space="preserve">Alwars </t>
   </si>
@@ -807,4 +808,55 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F2E8E6-7018-4BA1-AEC3-BB4BAF86B071}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6">
+      <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.6">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.6">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.6">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>